--- a/data/fmsForecastOutput/File1/RPT_RPT3913152273708ME_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT3913152273708ME_fmsForecastOutput.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1875,46 +1875,46 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>364.2184972485599</v>
+        <v>364.2184972485596</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>387.2779454412351</v>
+        <v>387.277945441235</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>481.2433810223013</v>
+        <v>481.2433810223011</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>465.8697956238066</v>
+        <v>465.8697956238065</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>454.3688268873256</v>
+        <v>454.3688268873255</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>364.2184972485599</v>
+        <v>364.2184972485596</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>387.2779454412351</v>
+        <v>387.277945441235</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>481.2433810223013</v>
+        <v>481.2433810223011</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>465.8697956238066</v>
+        <v>465.8697956238065</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>454.3688268873256</v>
+        <v>454.3688268873255</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>47045.02159219631</v>
+        <v>47045.02159219627</v>
       </c>
       <c r="N8" s="152" t="n">
-        <v>36789.21074430101</v>
+        <v>36789.210744301</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>28263.78239847889</v>
+        <v>28263.78239847888</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>26219.69839032407</v>
+        <v>26219.69839032406</v>
       </c>
       <c r="Q8" s="153" t="n">
         <v>26419.77349997146</v>
@@ -1925,46 +1925,46 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>338.0862283876767</v>
+        <v>338.0862283876765</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>359.4911870239268</v>
+        <v>359.4911870239267</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>446.7147079444681</v>
+        <v>446.7147079444679</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>432.4441600633542</v>
+        <v>432.444160063354</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>421.7683729402529</v>
+        <v>421.7683729402528</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>338.0862283876767</v>
+        <v>338.0862283876765</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>359.4911870239268</v>
+        <v>359.4911870239267</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>446.7147079444681</v>
+        <v>446.7147079444679</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>432.4441600633542</v>
+        <v>432.444160063354</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>421.7683729402529</v>
+        <v>421.7683729402528</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>47045.02159219631</v>
+        <v>47045.02159219627</v>
       </c>
       <c r="AE8" s="152" t="n">
-        <v>36789.21074430101</v>
+        <v>36789.210744301</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>28263.78239847889</v>
+        <v>28263.78239847888</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>26219.69839032407</v>
+        <v>26219.69839032406</v>
       </c>
       <c r="AH8" s="153" t="n">
         <v>26419.77349997146</v>
@@ -2025,7 +2025,7 @@
         <v>936.6295904912822</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>883.1288466851278</v>
+        <v>883.1288466851274</v>
       </c>
       <c r="E9" s="156" t="n">
         <v>997.123408743635</v>
@@ -2040,7 +2040,7 @@
         <v>936.6295904912822</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>883.1288466851278</v>
+        <v>883.1288466851274</v>
       </c>
       <c r="J9" s="156" t="n">
         <v>997.123408743635</v>
@@ -2055,7 +2055,7 @@
         <v>60120.11633089469</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>42691.38631060591</v>
+        <v>42691.38631060589</v>
       </c>
       <c r="O9" s="159" t="n">
         <v>34573.69262877763</v>
@@ -2064,7 +2064,7 @@
         <v>37476.24754127126</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>40740.64016530425</v>
+        <v>40740.64016530423</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>939.275436792105</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>885.6235609413005</v>
+        <v>885.6235609413002</v>
       </c>
       <c r="V9" s="156" t="n">
         <v>999.9401415366963</v>
@@ -2084,13 +2084,13 @@
         <v>1060.437358469889</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>1087.626385358827</v>
+        <v>1087.626385358826</v>
       </c>
       <c r="Y9" s="155" t="n">
         <v>939.275436792105</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>885.6235609413005</v>
+        <v>885.6235609413002</v>
       </c>
       <c r="AA9" s="156" t="n">
         <v>999.9401415366963</v>
@@ -2099,13 +2099,13 @@
         <v>1060.437358469889</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>1087.626385358827</v>
+        <v>1087.626385358826</v>
       </c>
       <c r="AD9" s="158" t="n">
         <v>60120.11633089469</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>42691.38631060591</v>
+        <v>42691.38631060589</v>
       </c>
       <c r="AF9" s="159" t="n">
         <v>34573.69262877763</v>
@@ -2114,7 +2114,7 @@
         <v>37476.24754127126</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>40740.64016530425</v>
+        <v>40740.64016530423</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2170,49 +2170,49 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>554.2410455523825</v>
+        <v>554.2410455523823</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>554.5078113043718</v>
+        <v>554.5078113043717</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>672.7480033938548</v>
+        <v>672.7480033938547</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>694.4504179191592</v>
+        <v>694.4504179191591</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>701.7058076123242</v>
+        <v>701.7058076123238</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>554.2410455523825</v>
+        <v>554.2410455523823</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>554.5078113043718</v>
+        <v>554.5078113043717</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>672.7480033938548</v>
+        <v>672.7480033938547</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>694.4504179191592</v>
+        <v>694.4504179191591</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>701.7058076123242</v>
+        <v>701.7058076123238</v>
       </c>
       <c r="M10" s="164" t="n">
         <v>107165.137923091</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>79480.59705490693</v>
+        <v>79480.5970549069</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>62837.47502725653</v>
+        <v>62837.47502725651</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>63695.94593159534</v>
+        <v>63695.94593159532</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>67160.41366527572</v>
+        <v>67160.41366527569</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>527.4968753679793</v>
+        <v>527.4968753679791</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>527.9637059491374</v>
+        <v>527.9637059491373</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>642.2073703692053</v>
+        <v>642.207370369205</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>663.6945547803028</v>
+        <v>663.6945547803026</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>670.9413488740391</v>
+        <v>670.9413488740389</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>527.4968753679793</v>
+        <v>527.4968753679791</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>527.9637059491374</v>
+        <v>527.9637059491373</v>
       </c>
       <c r="AA10" s="162" t="n">
-        <v>642.2073703692053</v>
+        <v>642.207370369205</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>663.6945547803028</v>
+        <v>663.6945547803026</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>670.9413488740391</v>
+        <v>670.9413488740389</v>
       </c>
       <c r="AD10" s="164" t="n">
         <v>107165.137923091</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>79480.59705490693</v>
+        <v>79480.5970549069</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>62837.47502725653</v>
+        <v>62837.47502725651</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>63695.94593159534</v>
+        <v>63695.94593159532</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>67160.41366527572</v>
+        <v>67160.41366527569</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2360,7 +2360,7 @@
         <v>92328.07945432008</v>
       </c>
       <c r="Q11" s="160" t="n">
-        <v>98791.2030271025</v>
+        <v>98791.20302710249</v>
       </c>
       <c r="S11" s="32" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>92328.07945432008</v>
       </c>
       <c r="AH11" s="160" t="n">
-        <v>98791.2030271025</v>
+        <v>98791.20302710249</v>
       </c>
       <c r="AJ11" s="39" t="n"/>
       <c r="AQ11" s="40" t="inlineStr">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>663.0723895950072</v>
+        <v>663.0723895950071</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>696.5462766183517</v>
+        <v>696.5462766183516</v>
       </c>
       <c r="E12" s="162" t="n">
         <v>849.4372201500537</v>
@@ -2473,13 +2473,13 @@
         <v>897.9519068353296</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>910.2024484420425</v>
+        <v>910.2024484420424</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>663.0723895950072</v>
+        <v>663.0723895950071</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>696.5462766183517</v>
+        <v>696.5462766183516</v>
       </c>
       <c r="J12" s="162" t="n">
         <v>849.4372201500537</v>
@@ -2488,7 +2488,7 @@
         <v>897.9519068353296</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>910.2024484420425</v>
+        <v>910.2024484420424</v>
       </c>
       <c r="M12" s="164" t="n">
         <v>180733.1765565019</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>657.1923777363595</v>
+        <v>657.1923777363594</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>696.2957908100148</v>
+        <v>696.2957908100146</v>
       </c>
       <c r="V12" s="162" t="n">
         <v>861.555025061308</v>
@@ -2523,13 +2523,13 @@
         <v>915.7450547498496</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>928.8675257166366</v>
+        <v>928.8675257166365</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>657.1923777363595</v>
+        <v>657.1923777363594</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>696.2957908100148</v>
+        <v>696.2957908100146</v>
       </c>
       <c r="AA12" s="162" t="n">
         <v>861.555025061308</v>
@@ -2538,7 +2538,7 @@
         <v>915.7450547498496</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>928.8675257166366</v>
+        <v>928.8675257166365</v>
       </c>
       <c r="AD12" s="164" t="n">
         <v>180733.1765565019</v>
@@ -2606,43 +2606,43 @@
         <v>3010.375343991182</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>3121.147162621986</v>
+        <v>3121.147162621985</v>
       </c>
       <c r="E13" s="156" t="n">
-        <v>3306.861072216792</v>
+        <v>3306.861072216791</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>3463.76811366028</v>
+        <v>3463.768113660278</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>3655.256336241924</v>
+        <v>3655.256336241922</v>
       </c>
       <c r="H13" s="155" t="n">
         <v>3010.375343991182</v>
       </c>
       <c r="I13" s="156" t="n">
-        <v>3121.147162621986</v>
+        <v>3121.147162621985</v>
       </c>
       <c r="J13" s="156" t="n">
-        <v>3306.861072216792</v>
+        <v>3306.861072216791</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>3463.76811366028</v>
+        <v>3463.768113660278</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>3655.256336241924</v>
+        <v>3655.256336241922</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>9338.202013880056</v>
+        <v>9338.202013880054</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>9912.166698132292</v>
+        <v>9912.166698132289</v>
       </c>
       <c r="O13" s="159" t="n">
         <v>10808.98361690807</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>11550.21106054366</v>
+        <v>11550.21106054365</v>
       </c>
       <c r="Q13" s="160" t="n">
         <v>12434.57634387655</v>
@@ -2653,46 +2653,46 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>826.0176248756293</v>
+        <v>826.0176248756291</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>856.4123312072522</v>
+        <v>856.412331207252</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>907.3704161570465</v>
+        <v>907.3704161570462</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>950.4241775287351</v>
+        <v>950.4241775287346</v>
       </c>
       <c r="X13" s="157" t="n">
         <v>1002.966677627357</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>826.0176248756293</v>
+        <v>826.0176248756291</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>856.4123312072522</v>
+        <v>856.412331207252</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>907.3704161570465</v>
+        <v>907.3704161570462</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>950.4241775287351</v>
+        <v>950.4241775287346</v>
       </c>
       <c r="AC13" s="157" t="n">
         <v>1002.966677627357</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>9338.202013880056</v>
+        <v>9338.202013880054</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>9912.166698132292</v>
+        <v>9912.166698132289</v>
       </c>
       <c r="AF13" s="159" t="n">
         <v>10808.98361690807</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>11550.21106054366</v>
+        <v>11550.21106054365</v>
       </c>
       <c r="AH13" s="160" t="n">
         <v>12434.57634387655</v>
@@ -2746,34 +2746,34 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>689.4855397090853</v>
+        <v>689.4855397090852</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>731.0486746720729</v>
+        <v>731.0486746720728</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>896.7931864434518</v>
+        <v>896.7931864434515</v>
       </c>
       <c r="F14" s="168" t="n">
         <v>946.2658603302756</v>
       </c>
       <c r="G14" s="169" t="n">
-        <v>960.4820765305921</v>
+        <v>960.4820765305917</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>689.4855397090853</v>
+        <v>689.4855397090852</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>731.0486746720729</v>
+        <v>731.0486746720728</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>896.7931864434518</v>
+        <v>896.7931864434515</v>
       </c>
       <c r="K14" s="168" t="n">
         <v>946.2658603302756</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>960.4820765305921</v>
+        <v>960.4820765305917</v>
       </c>
       <c r="M14" s="170" t="n">
         <v>190071.3785703819</v>
@@ -2788,7 +2788,7 @@
         <v>167574.2364464591</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>178386.1930362548</v>
+        <v>178386.1930362547</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2796,34 +2796,34 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>663.8584514043142</v>
+        <v>663.8584514043141</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>704.2957044617276</v>
+        <v>704.2957044617275</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>864.6573630442906</v>
+        <v>864.6573630442904</v>
       </c>
       <c r="W14" s="168" t="n">
-        <v>918.053935460073</v>
+        <v>918.0539354600729</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>933.6758373671204</v>
+        <v>933.6758373671203</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>663.8584514043142</v>
+        <v>663.8584514043141</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>704.2957044617276</v>
+        <v>704.2957044617275</v>
       </c>
       <c r="AA14" s="168" t="n">
-        <v>864.6573630442906</v>
+        <v>864.6573630442904</v>
       </c>
       <c r="AB14" s="168" t="n">
-        <v>918.053935460073</v>
+        <v>918.0539354600729</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>933.6758373671204</v>
+        <v>933.6758373671203</v>
       </c>
       <c r="AD14" s="170" t="n">
         <v>190071.3785703819</v>
@@ -2838,7 +2838,7 @@
         <v>167574.2364464591</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>178386.1930362548</v>
+        <v>178386.1930362547</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>3.334579764445652</v>
       </c>
       <c r="G24" s="81" t="n">
-        <v>3.401834290139253</v>
+        <v>3.401834290139254</v>
       </c>
       <c r="H24" s="79" t="n">
         <v>0</v>
@@ -3882,7 +3882,7 @@
         <v>3.334579764445652</v>
       </c>
       <c r="Q24" s="81" t="n">
-        <v>3.401834290139253</v>
+        <v>3.401834290139254</v>
       </c>
       <c r="S24" s="32" t="inlineStr">
         <is>
@@ -3896,13 +3896,13 @@
         <v>11.57405882299649</v>
       </c>
       <c r="V24" s="80" t="n">
-        <v>11.91242674925084</v>
+        <v>11.91242674925085</v>
       </c>
       <c r="W24" s="80" t="n">
         <v>12.15269069709082</v>
       </c>
       <c r="X24" s="81" t="n">
-        <v>12.39779607961861</v>
+        <v>12.39779607961862</v>
       </c>
       <c r="Y24" s="79" t="n">
         <v>0</v>
@@ -3926,13 +3926,13 @@
         <v>11.57405882299649</v>
       </c>
       <c r="AF24" s="80" t="n">
-        <v>11.91242674925084</v>
+        <v>11.91242674925085</v>
       </c>
       <c r="AG24" s="80" t="n">
         <v>12.15269069709082</v>
       </c>
       <c r="AH24" s="81" t="n">
-        <v>12.39779607961861</v>
+        <v>12.39779607961862</v>
       </c>
     </row>
     <row r="25" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -4408,46 +4408,46 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>370.9507945081135</v>
+        <v>370.9507945081132</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>404.7912747977797</v>
+        <v>404.7912747977796</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>506.6255294970563</v>
+        <v>506.625529497056</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>496.9178727528367</v>
+        <v>496.9178727528365</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>485.8455040695042</v>
+        <v>485.845504069504</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>370.9507945081135</v>
+        <v>370.9507945081132</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>404.7912747977797</v>
+        <v>404.7912747977796</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>506.6255294970563</v>
+        <v>506.625529497056</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>496.9178727528367</v>
+        <v>496.9178727528365</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>485.8455040695042</v>
+        <v>485.845504069504</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>47914.61243487291</v>
+        <v>47914.61243487287</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>38452.87781369275</v>
+        <v>38452.87781369274</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>29754.49489362511</v>
+        <v>29754.4948936251</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>27967.12057903376</v>
+        <v>27967.12057903375</v>
       </c>
       <c r="Q35" s="153" t="n">
         <v>28250.01939818115</v>
@@ -4458,46 +4458,46 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>344.3354908662757</v>
+        <v>344.3354908662755</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>375.7479546329166</v>
+        <v>375.7479546329165</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>470.2757157214828</v>
+        <v>470.2757157214826</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>461.2645724656376</v>
+        <v>461.2645724656375</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>450.9866338223649</v>
+        <v>450.9866338223648</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>344.3354908662757</v>
+        <v>344.3354908662755</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>375.7479546329166</v>
+        <v>375.7479546329165</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>470.2757157214828</v>
+        <v>470.2757157214826</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>461.2645724656376</v>
+        <v>461.2645724656375</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>450.9866338223649</v>
+        <v>450.9866338223648</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>47914.61243487291</v>
+        <v>47914.61243487287</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>38452.87781369275</v>
+        <v>38452.87781369274</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>29754.49489362511</v>
+        <v>29754.4948936251</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>27967.12057903376</v>
+        <v>27967.12057903375</v>
       </c>
       <c r="AH35" s="153" t="n">
         <v>28250.01939818115</v>
@@ -4513,7 +4513,7 @@
         <v>943.2290273246532</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>922.9150265861256</v>
+        <v>922.9150265861252</v>
       </c>
       <c r="E36" s="156" t="n">
         <v>1048.602898161903</v>
@@ -4528,7 +4528,7 @@
         <v>943.2290273246532</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>922.9150265861256</v>
+        <v>922.9150265861252</v>
       </c>
       <c r="J36" s="156" t="n">
         <v>1048.602898161903</v>
@@ -4543,7 +4543,7 @@
         <v>60543.71912346987</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>44614.69249899764</v>
+        <v>44614.69249899763</v>
       </c>
       <c r="O36" s="159" t="n">
         <v>36358.66330364742</v>
@@ -4552,7 +4552,7 @@
         <v>39906.64604224628</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>43490.15315934089</v>
+        <v>43490.15315934087</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         <v>945.8935161024064</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>925.5221311810017</v>
+        <v>925.5221311810013</v>
       </c>
       <c r="V36" s="156" t="n">
         <v>1051.565053241456</v>
@@ -4572,13 +4572,13 @@
         <v>1129.208527823621</v>
       </c>
       <c r="X36" s="157" t="n">
-        <v>1161.028346326243</v>
+        <v>1161.028346326242</v>
       </c>
       <c r="Y36" s="155" t="n">
         <v>945.8935161024064</v>
       </c>
       <c r="Z36" s="156" t="n">
-        <v>925.5221311810017</v>
+        <v>925.5221311810013</v>
       </c>
       <c r="AA36" s="156" t="n">
         <v>1051.565053241456</v>
@@ -4587,13 +4587,13 @@
         <v>1129.208527823621</v>
       </c>
       <c r="AC36" s="157" t="n">
-        <v>1161.028346326243</v>
+        <v>1161.028346326242</v>
       </c>
       <c r="AD36" s="158" t="n">
         <v>60543.71912346987</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>44614.69249899764</v>
+        <v>44614.69249899763</v>
       </c>
       <c r="AF36" s="159" t="n">
         <v>36358.66330364742</v>
@@ -4602,7 +4602,7 @@
         <v>39906.64604224628</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>43490.15315934089</v>
+        <v>43490.15315934087</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,49 +4612,49 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>560.9292373131958</v>
+        <v>560.9292373131956</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>579.5328458924585</v>
+        <v>579.5328458924582</v>
       </c>
       <c r="E37" s="162" t="n">
-        <v>707.8179884851278</v>
+        <v>707.8179884851276</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>739.9994600365119</v>
+        <v>739.9994600365118</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>749.5560699434956</v>
+        <v>749.5560699434953</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>560.9292373131958</v>
+        <v>560.9292373131956</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>579.5328458924585</v>
+        <v>579.5328458924582</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>707.8179884851278</v>
+        <v>707.8179884851276</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>739.9994600365119</v>
+        <v>739.9994600365118</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>749.5560699434956</v>
+        <v>749.5560699434953</v>
       </c>
       <c r="M37" s="164" t="n">
-        <v>108458.3315583428</v>
+        <v>108458.3315583427</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>83067.5703126904</v>
+        <v>83067.57031269037</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>66113.15819727254</v>
+        <v>66113.15819727253</v>
       </c>
       <c r="P37" s="165" t="n">
-        <v>67873.76662128004</v>
+        <v>67873.76662128002</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>71740.17255752205</v>
+        <v>71740.17255752202</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,49 +4662,49 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>533.8623372622254</v>
+        <v>533.8623372622252</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>551.7908004161246</v>
+        <v>551.7908004161245</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>675.6852889817236</v>
+        <v>675.6852889817234</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>707.2263180980186</v>
+        <v>707.2263180980184</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>716.6937414068794</v>
+        <v>716.6937414068792</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>533.8623372622254</v>
+        <v>533.8623372622252</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>551.7908004161246</v>
+        <v>551.7908004161245</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>675.6852889817236</v>
+        <v>675.6852889817234</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>707.2263180980186</v>
+        <v>707.2263180980184</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>716.6937414068794</v>
+        <v>716.6937414068792</v>
       </c>
       <c r="AD37" s="164" t="n">
-        <v>108458.3315583428</v>
+        <v>108458.3315583427</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>83067.5703126904</v>
+        <v>83067.57031269037</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>66113.15819727254</v>
+        <v>66113.15819727253</v>
       </c>
       <c r="AG37" s="165" t="n">
-        <v>67873.76662128004</v>
+        <v>67873.76662128002</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>71740.17255752205</v>
+        <v>71740.17255752202</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4726,7 +4726,7 @@
         <v>1198.770763160822</v>
       </c>
       <c r="G38" s="157" t="n">
-        <v>1216.27768615841</v>
+        <v>1216.277686158409</v>
       </c>
       <c r="H38" s="155" t="n">
         <v>946.2541837967573</v>
@@ -4741,7 +4741,7 @@
         <v>1198.770763160822</v>
       </c>
       <c r="L38" s="157" t="n">
-        <v>1216.27768615841</v>
+        <v>1216.277686158409</v>
       </c>
       <c r="M38" s="158" t="n">
         <v>74957.10010768488</v>
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>672.9130250492324</v>
+        <v>672.9130250492323</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>728.3489493440272</v>
+        <v>728.3489493440271</v>
       </c>
       <c r="E39" s="162" t="n">
         <v>893.8904911643054</v>
@@ -4828,13 +4828,13 @@
         <v>956.5962748077206</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>971.2739433169227</v>
+        <v>971.2739433169226</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>672.9130250492324</v>
+        <v>672.9130250492323</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>728.3489493440272</v>
+        <v>728.3489493440271</v>
       </c>
       <c r="J39" s="162" t="n">
         <v>893.8904911643054</v>
@@ -4843,7 +4843,7 @@
         <v>956.5962748077206</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>971.2739433169227</v>
+        <v>971.2739433169226</v>
       </c>
       <c r="M39" s="164" t="n">
         <v>183415.4316660276</v>
@@ -4866,10 +4866,10 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>666.9457481286165</v>
+        <v>666.9457481286164</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>728.0870269399429</v>
+        <v>728.0870269399428</v>
       </c>
       <c r="V39" s="162" t="n">
         <v>906.6424524947037</v>
@@ -4878,13 +4878,13 @@
         <v>975.5514759522001</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>991.191383923505</v>
+        <v>991.1913839235049</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>666.9457481286165</v>
+        <v>666.9457481286164</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>728.0870269399429</v>
+        <v>728.0870269399428</v>
       </c>
       <c r="AA39" s="162" t="n">
         <v>906.6424524947037</v>
@@ -4893,7 +4893,7 @@
         <v>975.5514759522001</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>991.191383923505</v>
+        <v>991.1913839235049</v>
       </c>
       <c r="AD39" s="164" t="n">
         <v>183415.4316660276</v>
@@ -4921,34 +4921,34 @@
         <v>3037.735167311229</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>3210.240228841176</v>
+        <v>3210.240228841175</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>3412.846786470453</v>
+        <v>3412.846786470452</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>3609.878029352035</v>
+        <v>3609.878029352033</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>3809.011307703916</v>
+        <v>3809.011307703915</v>
       </c>
       <c r="H40" s="155" t="n">
         <v>3037.735167311229</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>3210.240228841176</v>
+        <v>3210.240228841175</v>
       </c>
       <c r="J40" s="156" t="n">
-        <v>3412.846786470453</v>
+        <v>3412.846786470452</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>3609.878029352035</v>
+        <v>3609.878029352033</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>3809.011307703916</v>
+        <v>3809.011307703915</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>9423.072346656545</v>
+        <v>9423.072346656543</v>
       </c>
       <c r="N40" s="159" t="n">
         <v>10195.10924393346</v>
@@ -4968,37 +4968,37 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>833.5248934695446</v>
+        <v>833.5248934695444</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>880.8585993771519</v>
+        <v>880.8585993771517</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>936.4518621412826</v>
+        <v>936.4518621412823</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>990.5153129319606</v>
+        <v>990.5153129319601</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>1045.155541748026</v>
+        <v>1045.155541748025</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>833.5248934695446</v>
+        <v>833.5248934695444</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>880.8585993771519</v>
+        <v>880.8585993771517</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>936.4518621412826</v>
+        <v>936.4518621412823</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>990.5153129319606</v>
+        <v>990.5153129319601</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>1045.155541748026</v>
+        <v>1045.155541748025</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>9423.072346656545</v>
+        <v>9423.072346656543</v>
       </c>
       <c r="AE40" s="159" t="n">
         <v>10195.10924393346</v>
@@ -5020,10 +5020,10 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>699.5233107474115</v>
+        <v>699.5233107474114</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>763.6665974343124</v>
+        <v>763.6665974343123</v>
       </c>
       <c r="E41" s="180" t="n">
         <v>942.4322229110439</v>
@@ -5035,10 +5035,10 @@
         <v>1023.251203190941</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>699.5233107474115</v>
+        <v>699.5233107474114</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>763.6665974343124</v>
+        <v>763.6665974343123</v>
       </c>
       <c r="J41" s="180" t="n">
         <v>942.4322229110439</v>
@@ -5062,7 +5062,7 @@
         <v>178251.2293607279</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>190044.0321763624</v>
+        <v>190044.0321763623</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,34 +5070,34 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>673.5231343501899</v>
+        <v>673.5231343501898</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>735.7199634554458</v>
+        <v>735.7199634554457</v>
       </c>
       <c r="V41" s="186" t="n">
         <v>908.6609633397517</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>976.5477443634221</v>
+        <v>976.547744363422</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>994.693131002727</v>
+        <v>994.6931310027268</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>673.5231343501899</v>
+        <v>673.5231343501898</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>735.7199634554458</v>
+        <v>735.7199634554457</v>
       </c>
       <c r="AA41" s="186" t="n">
         <v>908.6609633397517</v>
       </c>
       <c r="AB41" s="186" t="n">
-        <v>976.5477443634221</v>
+        <v>976.547744363422</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>994.693131002727</v>
+        <v>994.6931310027268</v>
       </c>
       <c r="AD41" s="188" t="n">
         <v>192838.5040126842</v>
@@ -5112,7 +5112,7 @@
         <v>178251.2293607279</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>190044.0321763624</v>
+        <v>190044.0321763623</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.5319689580550878</v>
+        <v>0.5319689580550876</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.02764954899003751</v>
+        <v>0.0276495489900375</v>
       </c>
       <c r="E57" s="149" t="n">
         <v>0</v>
@@ -6349,10 +6349,10 @@
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.5319689580550878</v>
+        <v>0.5319689580550876</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.02764954899003751</v>
+        <v>0.0276495489900375</v>
       </c>
       <c r="J57" s="149" t="n">
         <v>0</v>
@@ -6364,10 +6364,10 @@
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>68.71285041023197</v>
+        <v>68.71285041023194</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>2.626550509145154</v>
+        <v>2.626550509145153</v>
       </c>
       <c r="O57" s="152" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         </is>
       </c>
       <c r="T57" s="148" t="n">
-        <v>0.4938007816923911</v>
+        <v>0.4938007816923908</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.02566572484725455</v>
+        <v>0.02566572484725454</v>
       </c>
       <c r="V57" s="149" t="n">
         <v>0</v>
@@ -6399,10 +6399,10 @@
         <v>0</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.4938007816923911</v>
+        <v>0.4938007816923908</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.02566572484725455</v>
+        <v>0.02566572484725454</v>
       </c>
       <c r="AA57" s="149" t="n">
         <v>0</v>
@@ -6414,10 +6414,10 @@
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>68.71285041023197</v>
+        <v>68.71285041023194</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>2.626550509145154</v>
+        <v>2.626550509145153</v>
       </c>
       <c r="AF57" s="152" t="n">
         <v>0</v>
@@ -6436,7 +6436,7 @@
         </is>
       </c>
       <c r="C58" s="155" t="n">
-        <v>8.97774493616725</v>
+        <v>8.977744936167248</v>
       </c>
       <c r="D58" s="156" t="n">
         <v>0.4900507240947735</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="H58" s="155" t="n">
-        <v>8.97774493616725</v>
+        <v>8.977744936167248</v>
       </c>
       <c r="I58" s="156" t="n">
         <v>0.4900507240947735</v>
@@ -6466,10 +6466,10 @@
         <v>0</v>
       </c>
       <c r="M58" s="158" t="n">
-        <v>576.2609631715446</v>
+        <v>576.2609631715445</v>
       </c>
       <c r="N58" s="159" t="n">
-        <v>23.68957242496385</v>
+        <v>23.68957242496384</v>
       </c>
       <c r="O58" s="159" t="n">
         <v>0</v>
@@ -6486,10 +6486,10 @@
         </is>
       </c>
       <c r="T58" s="155" t="n">
-        <v>9.00310579756885</v>
+        <v>9.003105797568848</v>
       </c>
       <c r="U58" s="156" t="n">
-        <v>0.4914350481741373</v>
+        <v>0.4914350481741372</v>
       </c>
       <c r="V58" s="156" t="n">
         <v>0</v>
@@ -6501,10 +6501,10 @@
         <v>0</v>
       </c>
       <c r="Y58" s="155" t="n">
-        <v>9.00310579756885</v>
+        <v>9.003105797568848</v>
       </c>
       <c r="Z58" s="156" t="n">
-        <v>0.4914350481741373</v>
+        <v>0.4914350481741372</v>
       </c>
       <c r="AA58" s="156" t="n">
         <v>0</v>
@@ -6516,10 +6516,10 @@
         <v>0</v>
       </c>
       <c r="AD58" s="158" t="n">
-        <v>576.2609631715446</v>
+        <v>576.2609631715445</v>
       </c>
       <c r="AE58" s="159" t="n">
-        <v>23.68957242496385</v>
+        <v>23.68957242496384</v>
       </c>
       <c r="AF58" s="159" t="n">
         <v>0</v>
@@ -6541,7 +6541,7 @@
         <v>3.335701961677283</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.1835982147961062</v>
+        <v>0.1835982147961061</v>
       </c>
       <c r="E59" s="162" t="n">
         <v>0</v>
@@ -6556,7 +6556,7 @@
         <v>3.335701961677283</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.1835982147961062</v>
+        <v>0.1835982147961061</v>
       </c>
       <c r="J59" s="162" t="n">
         <v>0</v>
@@ -6568,7 +6568,7 @@
         <v>0</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>644.9738135817765</v>
+        <v>644.9738135817764</v>
       </c>
       <c r="N59" s="165" t="n">
         <v>26.316122934109</v>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>644.9738135817765</v>
+        <v>644.9738135817764</v>
       </c>
       <c r="AE59" s="165" t="n">
         <v>26.316122934109</v>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>2.974796133805501</v>
+        <v>2.9747961338055</v>
       </c>
       <c r="D61" s="162" t="n">
         <v>0.1196192402496795</v>
@@ -6757,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>2.974796133805501</v>
+        <v>2.9747961338055</v>
       </c>
       <c r="I61" s="162" t="n">
         <v>0.1196192402496795</v>
@@ -6772,7 +6772,7 @@
         <v>0</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>810.8380974799034</v>
+        <v>810.8380974799031</v>
       </c>
       <c r="N61" s="165" t="n">
         <v>26.316122934109</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>2.948416153552487</v>
+        <v>2.948416153552486</v>
       </c>
       <c r="U61" s="162" t="n">
         <v>0.1195762238369982</v>
@@ -6807,7 +6807,7 @@
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>2.948416153552487</v>
+        <v>2.948416153552486</v>
       </c>
       <c r="Z61" s="162" t="n">
         <v>0.1195762238369982</v>
@@ -6822,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>810.8380974799034</v>
+        <v>810.8380974799031</v>
       </c>
       <c r="AE61" s="165" t="n">
         <v>26.316122934109</v>
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>2.941322083643452</v>
+        <v>2.941322083643451</v>
       </c>
       <c r="D63" s="180" t="n">
         <v>0.1179170423061735</v>
@@ -6961,7 +6961,7 @@
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>2.941322083643452</v>
+        <v>2.941322083643451</v>
       </c>
       <c r="I63" s="180" t="n">
         <v>0.1179170423061735</v>
@@ -6976,7 +6976,7 @@
         <v>0</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>810.8380974799034</v>
+        <v>810.8380974799031</v>
       </c>
       <c r="N63" s="183" t="n">
         <v>26.316122934109</v>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>2.831997788311445</v>
+        <v>2.831997788311444</v>
       </c>
       <c r="U63" s="186" t="n">
         <v>0.1136018287924849</v>
@@ -7011,7 +7011,7 @@
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>2.831997788311445</v>
+        <v>2.831997788311444</v>
       </c>
       <c r="Z63" s="186" t="n">
         <v>0.1136018287924849</v>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>810.8380974799034</v>
+        <v>810.8380974799031</v>
       </c>
       <c r="AE63" s="189" t="n">
         <v>26.316122934109</v>
@@ -7300,46 +7300,46 @@
         <v>1.242159160512869</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.7591585748340781</v>
+        <v>0.7591585748340779</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.5613739761420932</v>
+        <v>0.5613739761420931</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.2613110254668587</v>
+        <v>0.2613110254668586</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.277609737275925</v>
+        <v>0.2776097372759249</v>
       </c>
       <c r="H68" s="148" t="n">
         <v>1.242159160512869</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.7591585748340781</v>
+        <v>0.7591585748340779</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.5613739761420932</v>
+        <v>0.5613739761420931</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.2613110254668587</v>
+        <v>0.2613110254668586</v>
       </c>
       <c r="L68" s="150" t="n">
-        <v>0.277609737275925</v>
+        <v>0.2776097372759249</v>
       </c>
       <c r="M68" s="151" t="n">
         <v>160.4460096582956</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>72.11576369548776</v>
+        <v>72.11576369548774</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>32.96991196459434</v>
+        <v>32.96991196459433</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>14.70689093426431</v>
+        <v>14.7068909342643</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>16.14192247839948</v>
+        <v>16.14192247839947</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7350,46 +7350,46 @@
         <v>1.153035633301183</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.7046897981643684</v>
+        <v>0.7046897981643683</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.5210960226969206</v>
+        <v>0.5210960226969205</v>
       </c>
       <c r="W68" s="149" t="n">
         <v>0.2425622523391917</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.2576915498480559</v>
+        <v>0.2576915498480558</v>
       </c>
       <c r="Y68" s="148" t="n">
         <v>1.153035633301183</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.7046897981643684</v>
+        <v>0.7046897981643683</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.5210960226969206</v>
+        <v>0.5210960226969205</v>
       </c>
       <c r="AB68" s="149" t="n">
         <v>0.2425622523391917</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.2576915498480559</v>
+        <v>0.2576915498480558</v>
       </c>
       <c r="AD68" s="151" t="n">
         <v>160.4460096582956</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>72.11576369548776</v>
+        <v>72.11576369548774</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>32.96991196459434</v>
+        <v>32.96991196459433</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>14.70689093426431</v>
+        <v>14.7068909342643</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>16.14192247839948</v>
+        <v>16.14192247839947</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7408,10 +7408,10 @@
         <v>2.270717326691266</v>
       </c>
       <c r="F69" s="156" t="n">
-        <v>2.466453757338033</v>
+        <v>2.466453757338032</v>
       </c>
       <c r="G69" s="157" t="n">
-        <v>2.576551393678579</v>
+        <v>2.576551393678578</v>
       </c>
       <c r="H69" s="155" t="n">
         <v>6.191346922710103</v>
@@ -7423,25 +7423,25 @@
         <v>2.270717326691266</v>
       </c>
       <c r="K69" s="156" t="n">
-        <v>2.466453757338033</v>
+        <v>2.466453757338032</v>
       </c>
       <c r="L69" s="157" t="n">
-        <v>2.576551393678579</v>
+        <v>2.576551393678578</v>
       </c>
       <c r="M69" s="158" t="n">
         <v>397.4084323377169</v>
       </c>
       <c r="N69" s="159" t="n">
-        <v>69.31795906632779</v>
+        <v>69.31795906632777</v>
       </c>
       <c r="O69" s="159" t="n">
         <v>78.73356719082702</v>
       </c>
       <c r="P69" s="159" t="n">
-        <v>87.41161578976543</v>
+        <v>87.41161578976542</v>
       </c>
       <c r="Q69" s="160" t="n">
-        <v>96.78588257492852</v>
+        <v>96.78588257492851</v>
       </c>
       <c r="S69" s="32" t="inlineStr">
         <is>
@@ -7461,7 +7461,7 @@
         <v>2.473421140833338</v>
       </c>
       <c r="X69" s="157" t="n">
-        <v>2.583829787446033</v>
+        <v>2.583829787446032</v>
       </c>
       <c r="Y69" s="155" t="n">
         <v>6.208836603282729</v>
@@ -7476,22 +7476,22 @@
         <v>2.473421140833338</v>
       </c>
       <c r="AC69" s="157" t="n">
-        <v>2.583829787446033</v>
+        <v>2.583829787446032</v>
       </c>
       <c r="AD69" s="158" t="n">
         <v>397.4084323377169</v>
       </c>
       <c r="AE69" s="159" t="n">
-        <v>69.31795906632779</v>
+        <v>69.31795906632777</v>
       </c>
       <c r="AF69" s="159" t="n">
         <v>78.73356719082702</v>
       </c>
       <c r="AG69" s="159" t="n">
-        <v>87.41161578976543</v>
+        <v>87.41161578976542</v>
       </c>
       <c r="AH69" s="160" t="n">
-        <v>96.78588257492852</v>
+        <v>96.78588257492851</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" thickTop="1">
@@ -7504,7 +7504,7 @@
         <v>2.885134430749333</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.986732699039807</v>
+        <v>0.9867326990398068</v>
       </c>
       <c r="E70" s="162" t="n">
         <v>1.195915216856825</v>
@@ -7519,7 +7519,7 @@
         <v>2.885134430749333</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.986732699039807</v>
+        <v>0.9867326990398068</v>
       </c>
       <c r="J70" s="162" t="n">
         <v>1.195915216856825</v>
@@ -7554,7 +7554,7 @@
         <v>2.745916076497096</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.9394981313983595</v>
+        <v>0.9394981313983592</v>
       </c>
       <c r="V70" s="162" t="n">
         <v>1.141624445895984</v>
@@ -7569,7 +7569,7 @@
         <v>2.745916076497096</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.9394981313983595</v>
+        <v>0.9394981313983592</v>
       </c>
       <c r="AA70" s="162" t="n">
         <v>1.141624445895984</v>
@@ -7714,7 +7714,7 @@
         <v>1.338067269771478</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>1.688845198587652</v>
+        <v>1.688845198587651</v>
       </c>
       <c r="G72" s="163" t="n">
         <v>2.514242688885448</v>
@@ -7729,7 +7729,7 @@
         <v>1.338067269771478</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>1.688845198587652</v>
+        <v>1.688845198587651</v>
       </c>
       <c r="L72" s="163" t="n">
         <v>2.514242688885448</v>
@@ -7807,31 +7807,31 @@
         </is>
       </c>
       <c r="C73" s="155" t="n">
-        <v>43.91169408368146</v>
+        <v>43.91169408368145</v>
       </c>
       <c r="D73" s="156" t="n">
-        <v>58.39233312524617</v>
+        <v>58.39233312524615</v>
       </c>
       <c r="E73" s="156" t="n">
-        <v>72.19577991560119</v>
+        <v>72.19577991560116</v>
       </c>
       <c r="F73" s="156" t="n">
-        <v>85.70928655784053</v>
+        <v>85.7092865578405</v>
       </c>
       <c r="G73" s="157" t="n">
         <v>100.3205523725292</v>
       </c>
       <c r="H73" s="155" t="n">
-        <v>43.91169408368146</v>
+        <v>43.91169408368145</v>
       </c>
       <c r="I73" s="156" t="n">
-        <v>58.39233312524617</v>
+        <v>58.39233312524615</v>
       </c>
       <c r="J73" s="156" t="n">
-        <v>72.19577991560119</v>
+        <v>72.19577991560116</v>
       </c>
       <c r="K73" s="156" t="n">
-        <v>85.70928655784053</v>
+        <v>85.7092865578405</v>
       </c>
       <c r="L73" s="157" t="n">
         <v>100.3205523725292</v>
@@ -7846,10 +7846,10 @@
         <v>235.9830017880094</v>
       </c>
       <c r="P73" s="159" t="n">
-        <v>285.8044525808488</v>
+        <v>285.8044525808487</v>
       </c>
       <c r="Q73" s="160" t="n">
-        <v>341.2738950665808</v>
+        <v>341.2738950665807</v>
       </c>
       <c r="S73" s="32" t="inlineStr">
         <is>
@@ -7863,13 +7863,13 @@
         <v>16.02228652826876</v>
       </c>
       <c r="V73" s="156" t="n">
-        <v>19.80981765976862</v>
+        <v>19.80981765976861</v>
       </c>
       <c r="W73" s="156" t="n">
-        <v>23.5177920433099</v>
+        <v>23.51779204330989</v>
       </c>
       <c r="X73" s="157" t="n">
-        <v>27.5269808339257</v>
+        <v>27.52698083392569</v>
       </c>
       <c r="Y73" s="155" t="n">
         <v>12.04894044979064</v>
@@ -7878,13 +7878,13 @@
         <v>16.02228652826876</v>
       </c>
       <c r="AA73" s="156" t="n">
-        <v>19.80981765976862</v>
+        <v>19.80981765976861</v>
       </c>
       <c r="AB73" s="156" t="n">
-        <v>23.5177920433099</v>
+        <v>23.51779204330989</v>
       </c>
       <c r="AC73" s="157" t="n">
-        <v>27.5269808339257</v>
+        <v>27.52698083392569</v>
       </c>
       <c r="AD73" s="158" t="n">
         <v>136.2143331872573</v>
@@ -7896,10 +7896,10 @@
         <v>235.9830017880094</v>
       </c>
       <c r="AG73" s="159" t="n">
-        <v>285.8044525808488</v>
+        <v>285.8044525808487</v>
       </c>
       <c r="AH73" s="160" t="n">
-        <v>341.2738950665808</v>
+        <v>341.2738950665807</v>
       </c>
     </row>
     <row r="74" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -7915,13 +7915,13 @@
         <v>1.804893452021717</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>2.703536010078985</v>
+        <v>2.703536010078984</v>
       </c>
       <c r="F74" s="180" t="n">
         <v>3.270938134807355</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>4.305706564135105</v>
+        <v>4.305706564135104</v>
       </c>
       <c r="H74" s="179" t="n">
         <v>3.097294163919008</v>
@@ -7930,25 +7930,25 @@
         <v>1.804893452021717</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>2.703536010078985</v>
+        <v>2.703536010078984</v>
       </c>
       <c r="K74" s="180" t="n">
         <v>3.270938134807355</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>4.305706564135105</v>
+        <v>4.305706564135104</v>
       </c>
       <c r="M74" s="182" t="n">
         <v>853.8351244066375</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>402.806897437633</v>
+        <v>402.8068974376329</v>
       </c>
       <c r="O74" s="183" t="n">
-        <v>458.5708389187627</v>
+        <v>458.5708389187626</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>579.2504869748077</v>
+        <v>579.2504869748076</v>
       </c>
       <c r="Q74" s="184" t="n">
         <v>799.6803074990125</v>
@@ -7992,13 +7992,13 @@
         <v>853.8351244066375</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>402.806897437633</v>
+        <v>402.8068974376329</v>
       </c>
       <c r="AF74" s="189" t="n">
-        <v>458.5708389187627</v>
+        <v>458.5708389187626</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>579.2504869748077</v>
+        <v>579.2504869748076</v>
       </c>
       <c r="AH74" s="190" t="n">
         <v>799.6803074990125</v>
@@ -8260,46 +8260,46 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>372.7249226266814</v>
+        <v>372.7249226266811</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>405.5780829216038</v>
+        <v>405.5780829216037</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>507.1869034731984</v>
+        <v>507.1869034731981</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>497.1791837783035</v>
+        <v>497.1791837783034</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>486.1231138067801</v>
+        <v>486.12311380678</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>372.7249226266814</v>
+        <v>372.7249226266811</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>405.5780829216038</v>
+        <v>405.5780829216037</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>507.1869034731984</v>
+        <v>507.1869034731982</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>497.1791837783035</v>
+        <v>497.1791837783034</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>486.1231138067801</v>
+        <v>486.12311380678</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>48143.77129494143</v>
+        <v>48143.7712949414</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>38527.62012789738</v>
+        <v>38527.62012789737</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>29787.46480558971</v>
+        <v>29787.4648055897</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>27981.82746996802</v>
+        <v>27981.82746996801</v>
       </c>
       <c r="Q79" s="153" t="n">
         <v>28266.16132065955</v>
@@ -8310,46 +8310,46 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>345.9823272812693</v>
+        <v>345.9823272812691</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>376.4783101559282</v>
+        <v>376.4783101559281</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>470.7968117441796</v>
+        <v>470.7968117441795</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>461.5071347179768</v>
+        <v>461.5071347179766</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>451.2443253722129</v>
+        <v>451.2443253722128</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>345.9823272812693</v>
+        <v>345.9823272812691</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>376.4783101559282</v>
+        <v>376.4783101559281</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>470.7968117441796</v>
+        <v>470.7968117441795</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>461.5071347179768</v>
+        <v>461.5071347179766</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>451.2443253722129</v>
+        <v>451.2443253722128</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>48143.77129494143</v>
+        <v>48143.7712949414</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>38527.62012789738</v>
+        <v>38527.62012789737</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>29787.46480558971</v>
+        <v>29787.4648055897</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>27981.82746996802</v>
+        <v>27981.82746996801</v>
       </c>
       <c r="AH79" s="153" t="n">
         <v>28266.16132065955</v>
@@ -8365,7 +8365,7 @@
         <v>958.3981191835305</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>924.8390126900514</v>
+        <v>924.839012690051</v>
       </c>
       <c r="E80" s="156" t="n">
         <v>1050.873615488594</v>
@@ -8374,13 +8374,13 @@
         <v>1128.494112488498</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>1160.334395335904</v>
+        <v>1160.334395335903</v>
       </c>
       <c r="H80" s="155" t="n">
         <v>958.3981191835306</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>924.8390126900514</v>
+        <v>924.839012690051</v>
       </c>
       <c r="J80" s="156" t="n">
         <v>1050.873615488594</v>
@@ -8389,13 +8389,13 @@
         <v>1128.494112488498</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>1160.334395335904</v>
+        <v>1160.334395335903</v>
       </c>
       <c r="M80" s="158" t="n">
         <v>61517.38851897913</v>
       </c>
       <c r="N80" s="159" t="n">
-        <v>44707.70003048893</v>
+        <v>44707.70003048892</v>
       </c>
       <c r="O80" s="159" t="n">
         <v>36437.39687083825</v>
@@ -8404,7 +8404,7 @@
         <v>39994.05765803604</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>43586.93904191582</v>
+        <v>43586.9390419158</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>961.105458503258</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>927.4515522739216</v>
+        <v>927.4515522739213</v>
       </c>
       <c r="V80" s="156" t="n">
         <v>1053.842185023873</v>
@@ -8424,13 +8424,13 @@
         <v>1131.681948964454</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>1163.612176113689</v>
+        <v>1163.612176113688</v>
       </c>
       <c r="Y80" s="155" t="n">
         <v>961.105458503258</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>927.4515522739216</v>
+        <v>927.4515522739213</v>
       </c>
       <c r="AA80" s="156" t="n">
         <v>1053.842185023873</v>
@@ -8439,13 +8439,13 @@
         <v>1131.681948964454</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>1163.612176113689</v>
+        <v>1163.612176113688</v>
       </c>
       <c r="AD80" s="158" t="n">
         <v>61517.38851897913</v>
       </c>
       <c r="AE80" s="159" t="n">
-        <v>44707.70003048893</v>
+        <v>44707.70003048892</v>
       </c>
       <c r="AF80" s="159" t="n">
         <v>36437.39687083825</v>
@@ -8454,7 +8454,7 @@
         <v>39994.05765803604</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>43586.93904191582</v>
+        <v>43586.9390419158</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8464,49 +8464,49 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>567.1500737056224</v>
+        <v>567.1500737056222</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>580.7031768062943</v>
+        <v>580.7031768062941</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>709.0139037019845</v>
+        <v>709.0139037019844</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>741.1128156611845</v>
+        <v>741.1128156611843</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>750.7359628643726</v>
+        <v>750.7359628643724</v>
       </c>
       <c r="H81" s="161" t="n">
-        <v>567.1500737056224</v>
+        <v>567.1500737056222</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>580.7031768062943</v>
+        <v>580.7031768062941</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>709.0139037019845</v>
+        <v>709.0139037019844</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>741.1128156611845</v>
+        <v>741.1128156611843</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>750.7359628643726</v>
+        <v>750.7359628643724</v>
       </c>
       <c r="M81" s="164" t="n">
-        <v>109661.1598139206</v>
+        <v>109661.1598139205</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>83235.32015838631</v>
+        <v>83235.32015838628</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>66224.86167642796</v>
+        <v>66224.86167642794</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>67975.88512800407</v>
+        <v>67975.88512800405</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>71853.10036257537</v>
+        <v>71853.10036257535</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8514,49 +8514,49 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>539.7829954045866</v>
+        <v>539.7829954045864</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>552.9051079765577</v>
+        <v>552.9051079765575</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>676.8269134276195</v>
+        <v>676.8269134276194</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>708.2903653597991</v>
+        <v>708.290365359799</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>717.821905003749</v>
+        <v>717.8219050037488</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>539.7829954045866</v>
+        <v>539.7829954045864</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>552.9051079765577</v>
+        <v>552.9051079765575</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>676.8269134276195</v>
+        <v>676.8269134276194</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>708.2903653597991</v>
+        <v>708.290365359799</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>717.821905003749</v>
+        <v>717.8219050037488</v>
       </c>
       <c r="AD81" s="164" t="n">
-        <v>109661.1598139206</v>
+        <v>109661.1598139205</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>83235.32015838631</v>
+        <v>83235.32015838628</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>66224.86167642796</v>
+        <v>66224.86167642794</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>67975.88512800407</v>
+        <v>67975.88512800405</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>71853.10036257537</v>
+        <v>71853.10036257535</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8578,7 +8578,7 @@
         <v>1201.10305684808</v>
       </c>
       <c r="G82" s="157" t="n">
-        <v>1220.266418397676</v>
+        <v>1220.266418397675</v>
       </c>
       <c r="H82" s="155" t="n">
         <v>950.3649264551705</v>
@@ -8593,7 +8593,7 @@
         <v>1201.10305684808</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>1220.266418397676</v>
+        <v>1220.266418397675</v>
       </c>
       <c r="M82" s="158" t="n">
         <v>75282.73074080638</v>
@@ -8628,7 +8628,7 @@
         <v>1324.211929630927</v>
       </c>
       <c r="X82" s="157" t="n">
-        <v>1345.339468880055</v>
+        <v>1345.339468880054</v>
       </c>
       <c r="Y82" s="155" t="n">
         <v>1047.77401567627</v>
@@ -8643,7 +8643,7 @@
         <v>1324.211929630927</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>1345.339468880055</v>
+        <v>1345.339468880054</v>
       </c>
       <c r="AD82" s="158" t="n">
         <v>75282.73074080638</v>
@@ -8668,34 +8668,34 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>678.5206224313916</v>
+        <v>678.5206224313915</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>729.4565909415343</v>
+        <v>729.456590941534</v>
       </c>
       <c r="E83" s="162" t="n">
         <v>895.2285584340768</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>958.2851200063084</v>
+        <v>958.2851200063081</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>973.7881860058081</v>
+        <v>973.788186005808</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>678.5206224313916</v>
+        <v>678.5206224313915</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>729.4565909415343</v>
+        <v>729.456590941534</v>
       </c>
       <c r="J83" s="162" t="n">
         <v>895.2285584340768</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>958.2851200063084</v>
+        <v>958.2851200063081</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>973.7881860058081</v>
+        <v>973.788186005808</v>
       </c>
       <c r="M83" s="164" t="n">
         <v>184943.8905547269</v>
@@ -8721,31 +8721,31 @@
         <v>672.5036183020682</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>729.19427021718</v>
+        <v>729.1942702171799</v>
       </c>
       <c r="V83" s="162" t="n">
         <v>907.9996082123893</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>977.2737860526322</v>
+        <v>977.273786052632</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>993.7571849598279</v>
+        <v>993.7571849598277</v>
       </c>
       <c r="Y83" s="161" t="n">
         <v>672.5036183020682</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>729.19427021718</v>
+        <v>729.1942702171799</v>
       </c>
       <c r="AA83" s="162" t="n">
         <v>907.9996082123893</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>977.2737860526322</v>
+        <v>977.273786052632</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>993.7571849598279</v>
+        <v>993.7571849598277</v>
       </c>
       <c r="AD83" s="164" t="n">
         <v>184943.8905547269</v>
@@ -8773,37 +8773,37 @@
         <v>3081.646861394911</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>3268.632561966423</v>
+        <v>3268.632561966421</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>3485.042566386054</v>
+        <v>3485.042566386053</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>3695.587315909876</v>
+        <v>3695.587315909874</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>3909.331860076446</v>
+        <v>3909.331860076444</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>3081.646861394911</v>
+        <v>3081.64686139491</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>3268.632561966423</v>
+        <v>3268.632561966422</v>
       </c>
       <c r="J84" s="156" t="n">
-        <v>3485.042566386054</v>
+        <v>3485.042566386052</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>3695.587315909876</v>
+        <v>3695.587315909874</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>3909.331860076446</v>
+        <v>3909.331860076444</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>9559.286679843803</v>
+        <v>9559.286679843801</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>10380.55213069055</v>
+        <v>10380.55213069054</v>
       </c>
       <c r="O84" s="159" t="n">
         <v>11391.39721374559</v>
@@ -8820,13 +8820,13 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>845.5738339193352</v>
+        <v>845.5738339193351</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>896.8808859054208</v>
+        <v>896.8808859054204</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>956.2616798010512</v>
+        <v>956.2616798010508</v>
       </c>
       <c r="W84" s="156" t="n">
         <v>1014.03310497527</v>
@@ -8835,13 +8835,13 @@
         <v>1072.682522581951</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>845.5738339193352</v>
+        <v>845.5738339193351</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>896.8808859054208</v>
+        <v>896.8808859054204</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>956.2616798010512</v>
+        <v>956.2616798010508</v>
       </c>
       <c r="AB84" s="156" t="n">
         <v>1014.03310497527</v>
@@ -8850,10 +8850,10 @@
         <v>1072.682522581951</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>9559.286679843803</v>
+        <v>9559.286679843801</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>10380.55213069055</v>
+        <v>10380.55213069054</v>
       </c>
       <c r="AF84" s="159" t="n">
         <v>11391.39721374559</v>
@@ -8875,7 +8875,7 @@
         <v>705.5619269949739</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>765.5894079286403</v>
+        <v>765.5894079286402</v>
       </c>
       <c r="E85" s="180" t="n">
         <v>945.1357589211229</v>
@@ -8890,7 +8890,7 @@
         <v>705.5619269949739</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>765.5894079286403</v>
+        <v>765.5894079286402</v>
       </c>
       <c r="J85" s="180" t="n">
         <v>945.1357589211229</v>
@@ -8914,7 +8914,7 @@
         <v>178830.4798477027</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>190843.7124838614</v>
+        <v>190843.7124838613</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,34 +8922,34 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>679.3373047712595</v>
+        <v>679.3373047712594</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>737.5724080580662</v>
+        <v>737.5724080580661</v>
       </c>
       <c r="V85" s="186" t="n">
         <v>911.2676204293766</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>979.7211629059217</v>
+        <v>979.7211629059215</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>998.8786689528439</v>
+        <v>998.8786689528438</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>679.3373047712595</v>
+        <v>679.3373047712594</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>737.5724080580662</v>
+        <v>737.5724080580661</v>
       </c>
       <c r="AA85" s="186" t="n">
         <v>911.2676204293766</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>979.7211629059217</v>
+        <v>979.7211629059215</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>998.8786689528439</v>
+        <v>998.8786689528438</v>
       </c>
       <c r="AD85" s="188" t="n">
         <v>194503.1772345707</v>
@@ -8964,7 +8964,7 @@
         <v>178830.4798477027</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>190843.7124838614</v>
+        <v>190843.7124838613</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9880,7 +9880,7 @@
         <v>3.334579764445652</v>
       </c>
       <c r="G95" s="81" t="n">
-        <v>3.401834290139253</v>
+        <v>3.401834290139254</v>
       </c>
       <c r="H95" s="79" t="n">
         <v>0</v>
@@ -9910,7 +9910,7 @@
         <v>3.334579764445652</v>
       </c>
       <c r="Q95" s="81" t="n">
-        <v>3.401834290139253</v>
+        <v>3.401834290139254</v>
       </c>
       <c r="S95" s="32" t="inlineStr">
         <is>
@@ -9924,13 +9924,13 @@
         <v>11.57405882299649</v>
       </c>
       <c r="V95" s="80" t="n">
-        <v>11.91242674925084</v>
+        <v>11.91242674925085</v>
       </c>
       <c r="W95" s="80" t="n">
         <v>12.15269069709082</v>
       </c>
       <c r="X95" s="81" t="n">
-        <v>12.39779607961861</v>
+        <v>12.39779607961862</v>
       </c>
       <c r="Y95" s="79" t="n">
         <v>0</v>
@@ -9954,13 +9954,13 @@
         <v>11.57405882299649</v>
       </c>
       <c r="AF95" s="80" t="n">
-        <v>11.91242674925084</v>
+        <v>11.91242674925085</v>
       </c>
       <c r="AG95" s="80" t="n">
         <v>12.15269069709082</v>
       </c>
       <c r="AH95" s="81" t="n">
-        <v>12.39779607961861</v>
+        <v>12.39779607961862</v>
       </c>
       <c r="AJ95" s="120" t="n">
         <v>109.3333333333333</v>
